--- a/ig/main/CodeSystem-TRE-R64-AgregatCategorieEtablissementNiv2.xlsx
+++ b/ig/main/CodeSystem-TRE-R64-AgregatCategorieEtablissementNiv2.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>urn:ietf:rfc:3986#Uniform Resource Identifier (URI)#urn:oid:1.2.250.1.213.1.6.1.6</t>
+    <t>OID:1.2.250.1.213.1.6.1.6</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/main/CodeSystem-TRE-R64-AgregatCategorieEtablissementNiv2.xlsx
+++ b/ig/main/CodeSystem-TRE-R64-AgregatCategorieEtablissementNiv2.xlsx
@@ -76,7 +76,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ig/main/CodeSystem-TRE-R64-AgregatCategorieEtablissementNiv2.xlsx
+++ b/ig/main/CodeSystem-TRE-R64-AgregatCategorieEtablissementNiv2.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20231215120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/CodeSystem-TRE-R64-AgregatCategorieEtablissementNiv2.xlsx
+++ b/ig/main/CodeSystem-TRE-R64-AgregatCategorieEtablissementNiv2.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
